--- a/reports/summary.xlsx
+++ b/reports/summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_public_pages_reachable</t>
+          <t>test_dynamic_pages_and_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,23 +478,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>22.875</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_functional.py, line 7
-  @pytest.mark.functional
-  def test_public_pages_reachable(base_url):
-E       fixture 'base_url' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_functional.py:7"</t>
+          <t>Element 'logo' not present on https://xelta.ai/auth/login/: Message: 
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0xee4103
+	0xee4144
+	0xce</t>
         </is>
       </c>
     </row>
@@ -506,33 +505,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_login_flow</t>
+          <t>test_homepage_hash_stable</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tests.test_functional</t>
+          <t>tests.test_regression</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_functional.py, line 14
-  @pytest.mark.functional
-  def test_login_flow(browser, base_url):
-E       fixture 'browser' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_functional.py:14"</t>
+          <t>disabled by config: regression</t>
         </is>
       </c>
     </row>
@@ -544,12 +537,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_homepage_hash_stable</t>
+          <t>test_https_enforced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tests.test_regression</t>
+          <t>tests.test_security</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -559,18 +552,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_regression.py, line 6
-  @pytest.mark.regression
-  def test_homepage_hash_stable(base_url):
-E       fixture 'base_url' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_regression.py:6"</t>
+          <t>disabled by config: security</t>
         </is>
       </c>
     </row>
@@ -582,7 +569,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_https_enforced</t>
+          <t>test_basic_security_headers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -597,18 +584,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_security.py, line 4
-  @pytest.mark.security
-  def test_https_enforced(base_url):
-E       fixture 'base_url' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_security.py:4"</t>
+          <t>disabled by config: security</t>
         </is>
       </c>
     </row>
@@ -620,33 +601,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test_basic_security_headers</t>
+          <t>test_homepage_logo_visible</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tests.test_security</t>
+          <t>tests.test_ui</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_security.py, line 16
-  @pytest.mark.security
-  def test_basic_security_headers(base_url):
-E       fixture 'base_url' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_security.py:16"</t>
+          <t>disabled by config: ui</t>
         </is>
       </c>
     </row>
@@ -658,7 +633,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test_homepage_logo_visible</t>
+          <t>test_primary_cta_present</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -668,61 +643,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2.126</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_ui.py, line 4
-  @pytest.mark.ui
-  def test_homepage_logo_visible(browser, base_url):
-E       fixture 'browser' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_ui.py:4"</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>test_primary_cta_present</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>tests.test_ui</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>failed on setup with "file C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_ui.py, line 15
-  @pytest.mark.ui
-  def test_primary_cta_present(browser, base_url):
-E       fixture 'browser' not found
-&gt;       available fixtures: cache, capfd, capfdbinary, caplog, capsys, capsysbinary, capteesys, doctest_namespace, extra, extras, include_metadata_in_junit_xml, metadata, monkeypatch, pytestconfig, record_property, record_testsuite_property, record_xml_attribute, recwarn, subtests, tmp_path, tmp_path_factory, tmpdir, tmpdir_factory
-&gt;       use 'pytest --fixtures [testpath]' for help on them.
-C:\Users\amraw\Desktop\MatchbestSoftware\Automation_Framwork\dynamic-testing-framework\tests\test_ui.py:15"</t>
+          <t>disabled by config: ui</t>
         </is>
       </c>
     </row>

--- a/reports/summary.xlsx
+++ b/reports/summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.875</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,12 +488,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Element 'logo' not present on https://xelta.ai/auth/login/: Message: 
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0xee4103
-	0xee4144
-	0xce</t>
+          <t>disabled by config: functional</t>
         </is>
       </c>
     </row>
@@ -515,7 +510,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -547,19 +542,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>disabled by config: security</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -579,7 +570,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.825</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -589,7 +580,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>disabled by config: security</t>
+          <t>Missing recommended headers: content-security-policy, x-frame-options, x-content-type-options, referrer-policy</t>
         </is>
       </c>
     </row>
@@ -611,7 +602,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -643,7 +634,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.126</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
